--- a/livrables/marges_2x2_synthese.xlsx
+++ b/livrables/marges_2x2_synthese.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marges_2x2_synthese" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_2x2_synthese'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_2x2_synthese'!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,6 +476,11 @@
           <t>maximum</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>disp_iqr_pct_med</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,22 +489,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>42.2</v>
+        <v>38.5</v>
       </c>
       <c r="D2" t="n">
-        <v>36.2</v>
+        <v>34.6</v>
       </c>
       <c r="E2" t="n">
-        <v>49.6</v>
+        <v>45.7</v>
       </c>
       <c r="F2" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="G2" t="n">
-        <v>72.7</v>
+        <v>69.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3">
@@ -525,6 +534,9 @@
       <c r="G3" t="n">
         <v>69.59999999999999</v>
       </c>
+      <c r="H3" t="n">
+        <v>21.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,17 +554,20 @@
         <v>33.2</v>
       </c>
       <c r="E4" t="n">
-        <v>62.5</v>
+        <v>51.4</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>91.40000000000001</v>
+        <v>62.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/marges_2x2_synthese.xlsx
+++ b/livrables/marges_2x2_synthese.xlsx
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>38.5</v>
+        <v>36.8</v>
       </c>
       <c r="D2" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E2" t="n">
-        <v>45.7</v>
+        <v>44.3</v>
       </c>
       <c r="F2" t="n">
         <v>32.3</v>
@@ -507,7 +507,7 @@
         <v>69.8</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">

--- a/livrables/marges_2x2_synthese.xlsx
+++ b/livrables/marges_2x2_synthese.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marges_2x2_synthese" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_2x2_synthese'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_2x2_synthese'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,56 +427,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>cellule</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mediane</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>q25</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q75</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>minimum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>maximum</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>disp_iqr_pct_med</t>
         </is>
@@ -485,89 +491,230 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>11</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>36.8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>34.2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>44.3</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>32.3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>69.8</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>simple-CN</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>65.2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>63</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>60.8</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>21.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>42</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>33.2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>51.4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>24</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>62.5</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>81</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>simple-CN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>258.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>172</v>
+      </c>
+      <c r="H6" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>simple-MTX</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>104</v>
+      </c>
+      <c r="F7" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>166.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>simple-VIA</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>